--- a/output/roomself_excel/13501.xlsx
+++ b/output/roomself_excel/13501.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>186793</v>
+        <v>44145</v>
       </c>
       <c r="D2" t="n">
-        <v>4407</v>
+        <v>1752</v>
       </c>
       <c r="E2" t="n">
-        <v>585</v>
+        <v>213</v>
       </c>
       <c r="F2" t="n">
-        <v>461</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44145</v>
+        <v>31378</v>
       </c>
       <c r="D3" t="n">
-        <v>1752</v>
+        <v>1448</v>
       </c>
       <c r="E3" t="n">
-        <v>213</v>
+        <v>585</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31378</v>
+        <v>14247</v>
       </c>
       <c r="D4" t="n">
-        <v>1448</v>
+        <v>980</v>
       </c>
       <c r="E4" t="n">
-        <v>157</v>
+        <v>585</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14247</v>
+        <v>186793</v>
       </c>
       <c r="D5" t="n">
-        <v>980</v>
+        <v>4407</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>585</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13501.xlsx
+++ b/output/roomself_excel/13501.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>1752</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>213</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>46</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>162</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,26 @@
       <c r="D3" t="n">
         <v>1448</v>
       </c>
-      <c r="E3" t="n">
-        <v>585</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +605,42 @@
       <c r="D4" t="n">
         <v>980</v>
       </c>
-      <c r="E4" t="n">
-        <v>585</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>96</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +657,49 @@
       <c r="D5" t="n">
         <v>4407</v>
       </c>
-      <c r="E5" t="n">
-        <v>585</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>461</v>
+        <v>337</v>
+      </c>
+      <c r="G5" t="n">
+        <v>46</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>515</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>208</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>224</v>
+      </c>
+      <c r="P5" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
